--- a/summary_stats/chuuchuu_summary_2025_10.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_10.xlsx
@@ -1612,25 +1612,25 @@
         <v>87</v>
       </c>
       <c r="N15" t="n">
-        <v>1180</v>
+        <v>1157</v>
       </c>
       <c r="O15" t="n">
-        <v>998</v>
+        <v>976</v>
       </c>
       <c r="P15" t="n">
-        <v>923</v>
+        <v>901</v>
       </c>
       <c r="Q15" t="n">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="R15" t="n">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="S15" t="n">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="T15" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="U15" t="n">
         <v>1819</v>
@@ -1849,13 +1849,13 @@
         <v>12</v>
       </c>
       <c r="N18" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O18" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P18" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q18" t="n">
         <v>137</v>
@@ -2007,25 +2007,25 @@
         <v>765</v>
       </c>
       <c r="N20" t="n">
-        <v>3238</v>
+        <v>2873</v>
       </c>
       <c r="O20" t="n">
-        <v>2912</v>
+        <v>2563</v>
       </c>
       <c r="P20" t="n">
-        <v>2778</v>
+        <v>2435</v>
       </c>
       <c r="Q20" t="n">
-        <v>2305</v>
+        <v>1989</v>
       </c>
       <c r="R20" t="n">
-        <v>1861</v>
+        <v>1578</v>
       </c>
       <c r="S20" t="n">
-        <v>952</v>
+        <v>745</v>
       </c>
       <c r="T20" t="n">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="U20" t="n">
         <v>4433</v>
@@ -2086,25 +2086,25 @@
         <v>119</v>
       </c>
       <c r="N21" t="n">
-        <v>1400</v>
+        <v>1364</v>
       </c>
       <c r="O21" t="n">
-        <v>1192</v>
+        <v>1159</v>
       </c>
       <c r="P21" t="n">
-        <v>1119</v>
+        <v>1086</v>
       </c>
       <c r="Q21" t="n">
-        <v>876</v>
+        <v>844</v>
       </c>
       <c r="R21" t="n">
-        <v>662</v>
+        <v>634</v>
       </c>
       <c r="S21" t="n">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="T21" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="U21" t="n">
         <v>2014</v>
@@ -2244,25 +2244,25 @@
         <v>1806</v>
       </c>
       <c r="N23" t="n">
-        <v>10531</v>
+        <v>9880</v>
       </c>
       <c r="O23" t="n">
-        <v>9497</v>
+        <v>8880</v>
       </c>
       <c r="P23" t="n">
-        <v>9052</v>
+        <v>8448</v>
       </c>
       <c r="Q23" t="n">
-        <v>7603</v>
+        <v>7037</v>
       </c>
       <c r="R23" t="n">
-        <v>6177</v>
+        <v>5655</v>
       </c>
       <c r="S23" t="n">
-        <v>3460</v>
+        <v>3072</v>
       </c>
       <c r="T23" t="n">
-        <v>1059</v>
+        <v>880</v>
       </c>
       <c r="U23" t="n">
         <v>14750</v>
@@ -2323,25 +2323,25 @@
         <v>230</v>
       </c>
       <c r="N24" t="n">
-        <v>2403</v>
+        <v>2294</v>
       </c>
       <c r="O24" t="n">
-        <v>2123</v>
+        <v>2016</v>
       </c>
       <c r="P24" t="n">
-        <v>2027</v>
+        <v>1923</v>
       </c>
       <c r="Q24" t="n">
-        <v>1672</v>
+        <v>1576</v>
       </c>
       <c r="R24" t="n">
-        <v>1332</v>
+        <v>1242</v>
       </c>
       <c r="S24" t="n">
-        <v>663</v>
+        <v>593</v>
       </c>
       <c r="T24" t="n">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="U24" t="n">
         <v>3333</v>
@@ -2560,22 +2560,22 @@
         <v>5</v>
       </c>
       <c r="N27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
@@ -2639,25 +2639,25 @@
         <v>42</v>
       </c>
       <c r="N28" t="n">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="O28" t="n">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="P28" t="n">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="Q28" t="n">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="R28" t="n">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="S28" t="n">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="T28" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="U28" t="n">
         <v>729</v>
@@ -2797,19 +2797,19 @@
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -2876,25 +2876,25 @@
         <v>14</v>
       </c>
       <c r="N31" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="O31" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="P31" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="Q31" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="R31" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="S31" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="T31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U31" t="n">
         <v>429</v>
@@ -3113,10 +3113,10 @@
         <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O34" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P34" t="n">
         <v>240</v>
@@ -3587,25 +3587,25 @@
         <v>320</v>
       </c>
       <c r="N40" t="n">
-        <v>1091</v>
+        <v>952</v>
       </c>
       <c r="O40" t="n">
-        <v>1085</v>
+        <v>946</v>
       </c>
       <c r="P40" t="n">
-        <v>1081</v>
+        <v>942</v>
       </c>
       <c r="Q40" t="n">
-        <v>812</v>
+        <v>709</v>
       </c>
       <c r="R40" t="n">
-        <v>655</v>
+        <v>560</v>
       </c>
       <c r="S40" t="n">
-        <v>290</v>
+        <v>243</v>
       </c>
       <c r="T40" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="U40" t="n">
         <v>3642</v>
@@ -3745,25 +3745,25 @@
         <v>35</v>
       </c>
       <c r="N42" t="n">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="O42" t="n">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="P42" t="n">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="Q42" t="n">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="R42" t="n">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="S42" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="T42" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="U42" t="n">
         <v>472</v>
@@ -3824,16 +3824,16 @@
         <v>8</v>
       </c>
       <c r="N43" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P43" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="R43" t="n">
         <v>9</v>
@@ -4535,13 +4535,13 @@
         <v>11</v>
       </c>
       <c r="N52" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O52" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P52" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q52" t="n">
         <v>20</v>
@@ -4614,22 +4614,22 @@
         <v>4483</v>
       </c>
       <c r="N53" t="n">
-        <v>5958</v>
+        <v>5638</v>
       </c>
       <c r="O53" t="n">
-        <v>3582</v>
+        <v>3358</v>
       </c>
       <c r="P53" t="n">
-        <v>2832</v>
+        <v>2644</v>
       </c>
       <c r="Q53" t="n">
-        <v>1506</v>
+        <v>1387</v>
       </c>
       <c r="R53" t="n">
-        <v>724</v>
+        <v>654</v>
       </c>
       <c r="S53" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="T53" t="n">
         <v>6</v>
@@ -4693,22 +4693,22 @@
         <v>36</v>
       </c>
       <c r="N54" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O54" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="P54" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="Q54" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="R54" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="S54" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="T54" t="n">
         <v>24</v>
@@ -4772,22 +4772,22 @@
         <v>881</v>
       </c>
       <c r="N55" t="n">
-        <v>623</v>
+        <v>543</v>
       </c>
       <c r="O55" t="n">
-        <v>396</v>
+        <v>334</v>
       </c>
       <c r="P55" t="n">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="Q55" t="n">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="R55" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
@@ -5088,19 +5088,19 @@
         <v>216</v>
       </c>
       <c r="N59" t="n">
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="O59" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="P59" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q59" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="R59" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S59" t="n">
         <v>2</v>
@@ -5167,22 +5167,22 @@
         <v>4425</v>
       </c>
       <c r="N60" t="n">
-        <v>7690</v>
+        <v>7486</v>
       </c>
       <c r="O60" t="n">
-        <v>3724</v>
+        <v>3599</v>
       </c>
       <c r="P60" t="n">
-        <v>2767</v>
+        <v>2667</v>
       </c>
       <c r="Q60" t="n">
-        <v>1085</v>
+        <v>1037</v>
       </c>
       <c r="R60" t="n">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="S60" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="T60" t="n">
         <v>6</v>
@@ -5246,19 +5246,19 @@
         <v>1199</v>
       </c>
       <c r="N61" t="n">
-        <v>3607</v>
+        <v>3512</v>
       </c>
       <c r="O61" t="n">
-        <v>1320</v>
+        <v>1270</v>
       </c>
       <c r="P61" t="n">
-        <v>814</v>
+        <v>775</v>
       </c>
       <c r="Q61" t="n">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="R61" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="S61" t="n">
         <v>12</v>
@@ -5957,13 +5957,13 @@
         <v>32</v>
       </c>
       <c r="N70" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="O70" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P70" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q70" t="n">
         <v>57</v>
@@ -6115,16 +6115,16 @@
         <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O72" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R72" t="n">
         <v>5</v>
@@ -6431,25 +6431,25 @@
         <v>2</v>
       </c>
       <c r="N76" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O76" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P76" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q76" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R76" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S76" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T76" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U76" t="n">
         <v>654</v>
@@ -6510,19 +6510,19 @@
         <v>90</v>
       </c>
       <c r="N77" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="O77" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="P77" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="Q77" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R77" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S77" t="n">
         <v>11</v>
@@ -6589,22 +6589,22 @@
         <v>8</v>
       </c>
       <c r="N78" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O78" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P78" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q78" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="R78" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S78" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T78" t="n">
         <v>20</v>
@@ -6668,25 +6668,25 @@
         <v>9</v>
       </c>
       <c r="N79" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O79" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P79" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q79" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R79" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="S79" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="T79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U79" t="n">
         <v>889</v>
@@ -6747,22 +6747,22 @@
         <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O80" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P80" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q80" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R80" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S80" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T80" t="n">
         <v>9</v>
@@ -7774,10 +7774,10 @@
         <v>28</v>
       </c>
       <c r="N93" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O93" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P93" t="n">
         <v>239</v>
@@ -8485,22 +8485,22 @@
         <v>299</v>
       </c>
       <c r="N102" t="n">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="O102" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="P102" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="Q102" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="R102" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="S102" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T102" t="n">
         <v>11</v>
@@ -9670,22 +9670,22 @@
         <v>51</v>
       </c>
       <c r="N117" t="n">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="O117" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="P117" t="n">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="Q117" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="R117" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T117" t="n">
         <v>0</v>
@@ -9749,22 +9749,22 @@
         <v>629</v>
       </c>
       <c r="N118" t="n">
-        <v>6867</v>
+        <v>6766</v>
       </c>
       <c r="O118" t="n">
-        <v>4424</v>
+        <v>4337</v>
       </c>
       <c r="P118" t="n">
-        <v>3602</v>
+        <v>3527</v>
       </c>
       <c r="Q118" t="n">
-        <v>1916</v>
+        <v>1865</v>
       </c>
       <c r="R118" t="n">
-        <v>1012</v>
+        <v>983</v>
       </c>
       <c r="S118" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="T118" t="n">
         <v>9</v>
@@ -9828,22 +9828,22 @@
         <v>47</v>
       </c>
       <c r="N119" t="n">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="O119" t="n">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="P119" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q119" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="R119" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S119" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T119" t="n">
         <v>1</v>
@@ -9986,19 +9986,19 @@
         <v>8</v>
       </c>
       <c r="N121" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O121" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P121" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q121" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R121" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S121" t="n">
         <v>19</v>
@@ -10065,22 +10065,22 @@
         <v>140</v>
       </c>
       <c r="N122" t="n">
-        <v>3093</v>
+        <v>3082</v>
       </c>
       <c r="O122" t="n">
-        <v>1615</v>
+        <v>1605</v>
       </c>
       <c r="P122" t="n">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="Q122" t="n">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="R122" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="S122" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T122" t="n">
         <v>2</v>
@@ -10381,19 +10381,19 @@
         <v>52</v>
       </c>
       <c r="N126" t="n">
-        <v>1219</v>
+        <v>1211</v>
       </c>
       <c r="O126" t="n">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="P126" t="n">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="Q126" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R126" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="S126" t="n">
         <v>22</v>
@@ -10539,22 +10539,22 @@
         <v>370</v>
       </c>
       <c r="N128" t="n">
-        <v>5033</v>
+        <v>4990</v>
       </c>
       <c r="O128" t="n">
-        <v>2857</v>
+        <v>2825</v>
       </c>
       <c r="P128" t="n">
-        <v>2238</v>
+        <v>2209</v>
       </c>
       <c r="Q128" t="n">
-        <v>1057</v>
+        <v>1036</v>
       </c>
       <c r="R128" t="n">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="S128" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="T128" t="n">
         <v>11</v>
@@ -10618,19 +10618,19 @@
         <v>102</v>
       </c>
       <c r="N129" t="n">
-        <v>531</v>
+        <v>504</v>
       </c>
       <c r="O129" t="n">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="P129" t="n">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="Q129" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="R129" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="S129" t="n">
         <v>7</v>
@@ -11487,25 +11487,25 @@
         <v>3</v>
       </c>
       <c r="N140" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O140" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P140" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q140" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R140" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="S140" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T140" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U140" t="n">
         <v>544</v>
@@ -12356,22 +12356,22 @@
         <v>72</v>
       </c>
       <c r="N151" t="n">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="O151" t="n">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="P151" t="n">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="Q151" t="n">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="R151" t="n">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="S151" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="T151" t="n">
         <v>108</v>
@@ -12593,25 +12593,25 @@
         <v>5606</v>
       </c>
       <c r="N154" t="n">
-        <v>15170</v>
+        <v>15100</v>
       </c>
       <c r="O154" t="n">
-        <v>6707</v>
+        <v>6678</v>
       </c>
       <c r="P154" t="n">
-        <v>6703</v>
+        <v>6674</v>
       </c>
       <c r="Q154" t="n">
-        <v>4332</v>
+        <v>4314</v>
       </c>
       <c r="R154" t="n">
-        <v>3061</v>
+        <v>3047</v>
       </c>
       <c r="S154" t="n">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="T154" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="U154" t="n">
         <v>132215</v>
@@ -12672,16 +12672,16 @@
         <v>242</v>
       </c>
       <c r="N155" t="n">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="O155" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P155" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="Q155" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R155" t="n">
         <v>217</v>
@@ -13699,25 +13699,25 @@
         <v>36</v>
       </c>
       <c r="N168" t="n">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="O168" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P168" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q168" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R168" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S168" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T168" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U168" t="n">
         <v>1289</v>
@@ -14015,19 +14015,19 @@
         <v>19</v>
       </c>
       <c r="N172" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O172" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P172" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q172" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R172" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S172" t="n">
         <v>68</v>
@@ -14173,25 +14173,25 @@
         <v>127</v>
       </c>
       <c r="N174" t="n">
-        <v>3378</v>
+        <v>3364</v>
       </c>
       <c r="O174" t="n">
-        <v>2712</v>
+        <v>2698</v>
       </c>
       <c r="P174" t="n">
-        <v>2447</v>
+        <v>2433</v>
       </c>
       <c r="Q174" t="n">
-        <v>1758</v>
+        <v>1744</v>
       </c>
       <c r="R174" t="n">
-        <v>1242</v>
+        <v>1231</v>
       </c>
       <c r="S174" t="n">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="T174" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="U174" t="n">
         <v>6728</v>
@@ -14252,25 +14252,25 @@
         <v>132</v>
       </c>
       <c r="N175" t="n">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="O175" t="n">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="P175" t="n">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="Q175" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="R175" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="S175" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="T175" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U175" t="n">
         <v>3180</v>
@@ -14647,19 +14647,19 @@
         <v>256</v>
       </c>
       <c r="N180" t="n">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="O180" t="n">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="P180" t="n">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="Q180" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="R180" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="S180" t="n">
         <v>32</v>
@@ -15042,25 +15042,25 @@
         <v>8191</v>
       </c>
       <c r="N185" t="n">
-        <v>51802</v>
+        <v>51296</v>
       </c>
       <c r="O185" t="n">
-        <v>29773</v>
+        <v>29394</v>
       </c>
       <c r="P185" t="n">
-        <v>23444</v>
+        <v>23104</v>
       </c>
       <c r="Q185" t="n">
-        <v>11566</v>
+        <v>11313</v>
       </c>
       <c r="R185" t="n">
-        <v>6612</v>
+        <v>6435</v>
       </c>
       <c r="S185" t="n">
-        <v>2246</v>
+        <v>2164</v>
       </c>
       <c r="T185" t="n">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="U185" t="n">
         <v>229638</v>
@@ -15121,22 +15121,22 @@
         <v>202</v>
       </c>
       <c r="N186" t="n">
-        <v>1427</v>
+        <v>1415</v>
       </c>
       <c r="O186" t="n">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="P186" t="n">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="Q186" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="R186" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="S186" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T186" t="n">
         <v>5</v>
@@ -17461,25 +17461,25 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P3" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q3" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R3" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="T3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="U3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
         <v>539</v>
@@ -19645,22 +19645,22 @@
         <v>72</v>
       </c>
       <c r="O29" t="n">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="P29" t="n">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="Q29" t="n">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="R29" t="n">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="S29" t="n">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="T29" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="U29" t="n">
         <v>108</v>
@@ -19897,25 +19897,25 @@
         <v>5606</v>
       </c>
       <c r="O32" t="n">
-        <v>15170</v>
+        <v>15100</v>
       </c>
       <c r="P32" t="n">
-        <v>6707</v>
+        <v>6678</v>
       </c>
       <c r="Q32" t="n">
-        <v>6703</v>
+        <v>6674</v>
       </c>
       <c r="R32" t="n">
-        <v>4332</v>
+        <v>4314</v>
       </c>
       <c r="S32" t="n">
-        <v>3061</v>
+        <v>3047</v>
       </c>
       <c r="T32" t="n">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="U32" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="V32" t="n">
         <v>132215</v>
@@ -19981,16 +19981,16 @@
         <v>223</v>
       </c>
       <c r="O33" t="n">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="P33" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q33" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="R33" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="S33" t="n">
         <v>216</v>
@@ -20611,16 +20611,16 @@
         <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S2" t="n">
         <v>29</v>
@@ -21283,13 +21283,13 @@
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R10" t="n">
         <v>18</v>
@@ -21703,25 +21703,25 @@
         <v>763</v>
       </c>
       <c r="O15" t="n">
-        <v>3220</v>
+        <v>2855</v>
       </c>
       <c r="P15" t="n">
-        <v>2897</v>
+        <v>2548</v>
       </c>
       <c r="Q15" t="n">
-        <v>2763</v>
+        <v>2420</v>
       </c>
       <c r="R15" t="n">
-        <v>2296</v>
+        <v>1980</v>
       </c>
       <c r="S15" t="n">
-        <v>1855</v>
+        <v>1572</v>
       </c>
       <c r="T15" t="n">
-        <v>952</v>
+        <v>745</v>
       </c>
       <c r="U15" t="n">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="V15" t="n">
         <v>4413</v>
@@ -21787,25 +21787,25 @@
         <v>63</v>
       </c>
       <c r="O16" t="n">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="P16" t="n">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="Q16" t="n">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="R16" t="n">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="S16" t="n">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="T16" t="n">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="U16" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="V16" t="n">
         <v>663</v>
@@ -21955,25 +21955,25 @@
         <v>1806</v>
       </c>
       <c r="O18" t="n">
-        <v>10531</v>
+        <v>9880</v>
       </c>
       <c r="P18" t="n">
-        <v>9497</v>
+        <v>8880</v>
       </c>
       <c r="Q18" t="n">
-        <v>9052</v>
+        <v>8448</v>
       </c>
       <c r="R18" t="n">
-        <v>7603</v>
+        <v>7037</v>
       </c>
       <c r="S18" t="n">
-        <v>6177</v>
+        <v>5655</v>
       </c>
       <c r="T18" t="n">
-        <v>3460</v>
+        <v>3072</v>
       </c>
       <c r="U18" t="n">
-        <v>1059</v>
+        <v>880</v>
       </c>
       <c r="V18" t="n">
         <v>14750</v>
@@ -22039,19 +22039,19 @@
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
         <v>3</v>
@@ -22207,25 +22207,25 @@
         <v>19</v>
       </c>
       <c r="O21" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P21" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q21" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R21" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="S21" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="U21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V21" t="n">
         <v>357</v>
@@ -22795,25 +22795,25 @@
         <v>32</v>
       </c>
       <c r="O28" t="n">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="P28" t="n">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="Q28" t="n">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="R28" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="S28" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="T28" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="U28" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="V28" t="n">
         <v>451</v>
@@ -22963,25 +22963,25 @@
         <v>20</v>
       </c>
       <c r="O30" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="P30" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q30" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="R30" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="S30" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="T30" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="U30" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="V30" t="n">
         <v>225</v>
@@ -23047,25 +23047,25 @@
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q31" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V31" t="n">
         <v>152</v>
@@ -23131,25 +23131,25 @@
         <v>45</v>
       </c>
       <c r="O32" t="n">
-        <v>552</v>
+        <v>522</v>
       </c>
       <c r="P32" t="n">
-        <v>508</v>
+        <v>478</v>
       </c>
       <c r="Q32" t="n">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="R32" t="n">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="S32" t="n">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="T32" t="n">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="U32" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="V32" t="n">
         <v>678</v>
@@ -23215,22 +23215,22 @@
         <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P33" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q33" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R33" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S33" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="T33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33" t="n">
         <v>2</v>
@@ -23719,25 +23719,25 @@
         <v>11</v>
       </c>
       <c r="O39" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P39" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="Q39" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="R39" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T39" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
         <v>235</v>
@@ -23803,22 +23803,22 @@
         <v>22</v>
       </c>
       <c r="O40" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="P40" t="n">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="Q40" t="n">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="R40" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="S40" t="n">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="T40" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="U40" t="n">
         <v>23</v>
@@ -23887,25 +23887,25 @@
         <v>16</v>
       </c>
       <c r="O41" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P41" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q41" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="R41" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="S41" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="T41" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="U41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V41" t="n">
         <v>107</v>
@@ -23971,25 +23971,25 @@
         <v>25</v>
       </c>
       <c r="O42" t="n">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="P42" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="Q42" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="R42" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="S42" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="T42" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="U42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V42" t="n">
         <v>234</v>
@@ -24055,25 +24055,25 @@
         <v>144</v>
       </c>
       <c r="O43" t="n">
-        <v>946</v>
+        <v>885</v>
       </c>
       <c r="P43" t="n">
-        <v>853</v>
+        <v>794</v>
       </c>
       <c r="Q43" t="n">
-        <v>818</v>
+        <v>760</v>
       </c>
       <c r="R43" t="n">
-        <v>689</v>
+        <v>637</v>
       </c>
       <c r="S43" t="n">
-        <v>569</v>
+        <v>521</v>
       </c>
       <c r="T43" t="n">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="U43" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="V43" t="n">
         <v>1299</v>
@@ -24223,19 +24223,19 @@
         <v>7</v>
       </c>
       <c r="O45" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P45" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q45" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R45" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S45" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="T45" t="n">
         <v>30</v>
@@ -24391,10 +24391,10 @@
         <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P47" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q47" t="n">
         <v>240</v>
@@ -24559,22 +24559,22 @@
         <v>5</v>
       </c>
       <c r="O49" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U49" t="n">
         <v>2</v>
@@ -24643,25 +24643,25 @@
         <v>42</v>
       </c>
       <c r="O50" t="n">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="P50" t="n">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="Q50" t="n">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="R50" t="n">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="S50" t="n">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="T50" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="U50" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="V50" t="n">
         <v>727</v>
@@ -25063,22 +25063,22 @@
         <v>27</v>
       </c>
       <c r="O55" t="n">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="P55" t="n">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="Q55" t="n">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="R55" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="S55" t="n">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="T55" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="U55" t="n">
         <v>15</v>
@@ -25609,22 +25609,22 @@
         <v>35</v>
       </c>
       <c r="O2" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P2" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="Q2" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="R2" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="S2" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="T2" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="U2" t="n">
         <v>21</v>
@@ -25861,22 +25861,22 @@
         <v>4483</v>
       </c>
       <c r="O5" t="n">
-        <v>5958</v>
+        <v>5638</v>
       </c>
       <c r="P5" t="n">
-        <v>3582</v>
+        <v>3358</v>
       </c>
       <c r="Q5" t="n">
-        <v>2832</v>
+        <v>2644</v>
       </c>
       <c r="R5" t="n">
-        <v>1506</v>
+        <v>1387</v>
       </c>
       <c r="S5" t="n">
-        <v>724</v>
+        <v>654</v>
       </c>
       <c r="T5" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="U5" t="n">
         <v>6</v>
@@ -25945,22 +25945,22 @@
         <v>881</v>
       </c>
       <c r="O6" t="n">
-        <v>623</v>
+        <v>543</v>
       </c>
       <c r="P6" t="n">
-        <v>396</v>
+        <v>334</v>
       </c>
       <c r="Q6" t="n">
-        <v>327</v>
+        <v>275</v>
       </c>
       <c r="R6" t="n">
-        <v>182</v>
+        <v>149</v>
       </c>
       <c r="S6" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="T6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -26113,19 +26113,19 @@
         <v>216</v>
       </c>
       <c r="O8" t="n">
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="P8" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="Q8" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="R8" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -26197,22 +26197,22 @@
         <v>4425</v>
       </c>
       <c r="O9" t="n">
-        <v>7690</v>
+        <v>7486</v>
       </c>
       <c r="P9" t="n">
-        <v>3724</v>
+        <v>3599</v>
       </c>
       <c r="Q9" t="n">
-        <v>2767</v>
+        <v>2667</v>
       </c>
       <c r="R9" t="n">
-        <v>1085</v>
+        <v>1037</v>
       </c>
       <c r="S9" t="n">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="T9" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="U9" t="n">
         <v>6</v>
@@ -26281,19 +26281,19 @@
         <v>1199</v>
       </c>
       <c r="O10" t="n">
-        <v>3607</v>
+        <v>3512</v>
       </c>
       <c r="P10" t="n">
-        <v>1320</v>
+        <v>1270</v>
       </c>
       <c r="Q10" t="n">
-        <v>814</v>
+        <v>775</v>
       </c>
       <c r="R10" t="n">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="S10" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="T10" t="n">
         <v>12</v>
@@ -26365,13 +26365,13 @@
         <v>11</v>
       </c>
       <c r="O11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R11" t="n">
         <v>20</v>
@@ -27163,22 +27163,22 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P8" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
@@ -29851,13 +29851,13 @@
         <v>32</v>
       </c>
       <c r="O40" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="P40" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q40" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R40" t="n">
         <v>57</v>
@@ -29935,16 +29935,16 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -30187,25 +30187,25 @@
         <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P44" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q44" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R44" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="S44" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="T44" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U44" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="V44" t="n">
         <v>652</v>
@@ -30271,19 +30271,19 @@
         <v>90</v>
       </c>
       <c r="O45" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="P45" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="Q45" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="R45" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="S45" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T45" t="n">
         <v>11</v>
@@ -30439,25 +30439,25 @@
         <v>9</v>
       </c>
       <c r="O47" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="P47" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="Q47" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R47" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="S47" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="T47" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="U47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
         <v>889</v>
@@ -30523,22 +30523,22 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="P48" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q48" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R48" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S48" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="T48" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U48" t="n">
         <v>9</v>
@@ -32245,22 +32245,22 @@
         <v>297</v>
       </c>
       <c r="O12" t="n">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="P12" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="Q12" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="R12" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="S12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="T12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U12" t="n">
         <v>11</v>
@@ -34345,10 +34345,10 @@
         <v>15</v>
       </c>
       <c r="O37" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P37" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q37" t="n">
         <v>54</v>
@@ -34891,19 +34891,19 @@
         <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P2" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q2" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R2" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T2" t="n">
         <v>19</v>
@@ -34975,22 +34975,22 @@
         <v>51</v>
       </c>
       <c r="O3" t="n">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="P3" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="Q3" t="n">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="R3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="S3" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -35143,22 +35143,22 @@
         <v>629</v>
       </c>
       <c r="O5" t="n">
-        <v>6867</v>
+        <v>6766</v>
       </c>
       <c r="P5" t="n">
-        <v>4424</v>
+        <v>4337</v>
       </c>
       <c r="Q5" t="n">
-        <v>3602</v>
+        <v>3527</v>
       </c>
       <c r="R5" t="n">
-        <v>1916</v>
+        <v>1865</v>
       </c>
       <c r="S5" t="n">
-        <v>1012</v>
+        <v>983</v>
       </c>
       <c r="T5" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="U5" t="n">
         <v>9</v>
@@ -35227,22 +35227,22 @@
         <v>33</v>
       </c>
       <c r="O6" t="n">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="P6" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q6" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="R6" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="S6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -35395,22 +35395,22 @@
         <v>140</v>
       </c>
       <c r="O8" t="n">
-        <v>3093</v>
+        <v>3082</v>
       </c>
       <c r="P8" t="n">
-        <v>1615</v>
+        <v>1605</v>
       </c>
       <c r="Q8" t="n">
-        <v>1265</v>
+        <v>1257</v>
       </c>
       <c r="R8" t="n">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="S8" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="T8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
@@ -35563,19 +35563,19 @@
         <v>52</v>
       </c>
       <c r="O10" t="n">
-        <v>1219</v>
+        <v>1211</v>
       </c>
       <c r="P10" t="n">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="Q10" t="n">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="R10" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="S10" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="T10" t="n">
         <v>22</v>
@@ -35731,22 +35731,22 @@
         <v>370</v>
       </c>
       <c r="O12" t="n">
-        <v>5033</v>
+        <v>4990</v>
       </c>
       <c r="P12" t="n">
-        <v>2857</v>
+        <v>2825</v>
       </c>
       <c r="Q12" t="n">
-        <v>2238</v>
+        <v>2209</v>
       </c>
       <c r="R12" t="n">
-        <v>1057</v>
+        <v>1036</v>
       </c>
       <c r="S12" t="n">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="T12" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="U12" t="n">
         <v>11</v>
@@ -35815,19 +35815,19 @@
         <v>101</v>
       </c>
       <c r="O13" t="n">
-        <v>499</v>
+        <v>472</v>
       </c>
       <c r="P13" t="n">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="Q13" t="n">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="R13" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="S13" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="T13" t="n">
         <v>6</v>
@@ -35899,19 +35899,19 @@
         <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q14" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="S14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
@@ -37705,25 +37705,25 @@
         <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P19" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q19" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R19" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S19" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19" t="n">
         <v>923</v>
@@ -38209,19 +38209,19 @@
         <v>19</v>
       </c>
       <c r="O25" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P25" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q25" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R25" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S25" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="T25" t="n">
         <v>68</v>
@@ -38377,25 +38377,25 @@
         <v>127</v>
       </c>
       <c r="O27" t="n">
-        <v>3378</v>
+        <v>3364</v>
       </c>
       <c r="P27" t="n">
-        <v>2712</v>
+        <v>2698</v>
       </c>
       <c r="Q27" t="n">
-        <v>2447</v>
+        <v>2433</v>
       </c>
       <c r="R27" t="n">
-        <v>1758</v>
+        <v>1744</v>
       </c>
       <c r="S27" t="n">
-        <v>1242</v>
+        <v>1231</v>
       </c>
       <c r="T27" t="n">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="U27" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="V27" t="n">
         <v>6728</v>
@@ -38461,25 +38461,25 @@
         <v>132</v>
       </c>
       <c r="O28" t="n">
-        <v>1388</v>
+        <v>1381</v>
       </c>
       <c r="P28" t="n">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="Q28" t="n">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="R28" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="S28" t="n">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="T28" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="U28" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="V28" t="n">
         <v>3180</v>
@@ -38713,19 +38713,19 @@
         <v>256</v>
       </c>
       <c r="O31" t="n">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="P31" t="n">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="Q31" t="n">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="R31" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="S31" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T31" t="n">
         <v>32</v>
@@ -38965,25 +38965,25 @@
         <v>8191</v>
       </c>
       <c r="O34" t="n">
-        <v>51802</v>
+        <v>51296</v>
       </c>
       <c r="P34" t="n">
-        <v>29773</v>
+        <v>29394</v>
       </c>
       <c r="Q34" t="n">
-        <v>23444</v>
+        <v>23104</v>
       </c>
       <c r="R34" t="n">
-        <v>11566</v>
+        <v>11313</v>
       </c>
       <c r="S34" t="n">
-        <v>6612</v>
+        <v>6435</v>
       </c>
       <c r="T34" t="n">
-        <v>2246</v>
+        <v>2164</v>
       </c>
       <c r="U34" t="n">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="V34" t="n">
         <v>229638</v>
@@ -39049,22 +39049,22 @@
         <v>202</v>
       </c>
       <c r="O35" t="n">
-        <v>1427</v>
+        <v>1415</v>
       </c>
       <c r="P35" t="n">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="Q35" t="n">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="R35" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="S35" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="T35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="U35" t="n">
         <v>5</v>

--- a/summary_stats/chuuchuu_summary_2025_10.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_10.xlsx
@@ -16918,40 +16918,40 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>218</v>
+        <v>320</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N209" t="n">
-        <v>158</v>
+        <v>239</v>
       </c>
       <c r="O209" t="n">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="P209" t="n">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="Q209" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="R209" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="S209" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="T209" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U209" t="n">
-        <v>218</v>
+        <v>320</v>
       </c>
     </row>
     <row r="210">
